--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
